--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1404,13 +1404,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA089164-A805-46AD-8DC8-67365AC0152B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD49A637-315F-4609-AF6A-7468D3BBFA35}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{167041F4-80BE-44DA-BFB3-0E5713245372}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB9070AE-F720-47A3-8A86-ED4E9352CC5C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3CE16A5F-45CA-4378-AACD-B04B0DB0CE72}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B856456E-FD68-4152-9C6E-27BA288B0318}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1404,13 +1404,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD49A637-315F-4609-AF6A-7468D3BBFA35}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28A3266B-B893-4294-8515-4D8FAD0A8919}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB9070AE-F720-47A3-8A86-ED4E9352CC5C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9780D9DD-1B2A-4E99-B1F0-A1D17B790A73}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B856456E-FD68-4152-9C6E-27BA288B0318}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A120370-22D6-4EEE-B021-11059852A250}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1404,13 +1404,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28A3266B-B893-4294-8515-4D8FAD0A8919}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33A824EB-292C-4D1B-B863-141F30A8DDB9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9780D9DD-1B2A-4E99-B1F0-A1D17B790A73}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810383C1-D71A-4132-881C-7B3733DA6818}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A120370-22D6-4EEE-B021-11059852A250}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DDDA957-F6F1-43FB-BEFE-7B0B11166CCD}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1395,22 +1395,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD49A637-315F-4609-AF6A-7468D3BBFA35}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA19B91F-7932-4266-9EF9-85A922ED8407}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB9070AE-F720-47A3-8A86-ED4E9352CC5C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24C9879C-5CF1-4BD3-B170-9BBC7ED4B1A9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B856456E-FD68-4152-9C6E-27BA288B0318}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BC5E7CD-32EA-4E11-BEE9-BD884BF37B7A}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1395,22 +1395,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33A824EB-292C-4D1B-B863-141F30A8DDB9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DF15634-9D3B-400C-90FF-3BD76EEA23EB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810383C1-D71A-4132-881C-7B3733DA6818}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA91837D-094D-41BC-B91C-7BDDE5D2C3FC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DDDA957-F6F1-43FB-BEFE-7B0B11166CCD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37A703F7-56C8-4F11-873C-847360942B8C}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1404,13 +1404,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DF15634-9D3B-400C-90FF-3BD76EEA23EB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{153A63BE-825F-471A-8124-C211ABAAACE4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA91837D-094D-41BC-B91C-7BDDE5D2C3FC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E06C037-19E2-4553-8E7F-098F1D1A539A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37A703F7-56C8-4F11-873C-847360942B8C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E83A7B38-FD02-45B8-B52C-2B07DAD081D7}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1404,13 +1404,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{153A63BE-825F-471A-8124-C211ABAAACE4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CA47273-5F80-4F54-BAE8-C08CCB078725}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E06C037-19E2-4553-8E7F-098F1D1A539A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB1522B2-E2F8-469A-814F-9FD40E25E1DB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E83A7B38-FD02-45B8-B52C-2B07DAD081D7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2BEC3FA-56E1-4F9D-A094-A22082CE5F29}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1404,13 +1404,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CA47273-5F80-4F54-BAE8-C08CCB078725}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{859F8AE2-6027-4DD7-9E21-AE7452920296}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB1522B2-E2F8-469A-814F-9FD40E25E1DB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CF222D2-076B-4D18-82CF-A75E5E4FD614}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D2BEC3FA-56E1-4F9D-A094-A22082CE5F29}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7033E223-CB3F-42EE-9F0D-0FFE3A02E652}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1404,13 +1404,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{859F8AE2-6027-4DD7-9E21-AE7452920296}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FE9C270-F312-4440-9350-1D1F60AAFB83}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CF222D2-076B-4D18-82CF-A75E5E4FD614}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4870A4C1-3F2A-423E-942C-E7CDFF19B2EF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7033E223-CB3F-42EE-9F0D-0FFE3A02E652}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEED9394-B763-417F-9F25-03317433D419}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1404,13 +1404,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FE9C270-F312-4440-9350-1D1F60AAFB83}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08E78BF0-F3C6-4FA0-9F10-5BFC004961C1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4870A4C1-3F2A-423E-942C-E7CDFF19B2EF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA6287E7-B9E1-4FFA-874F-F8BA58FF1439}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEED9394-B763-417F-9F25-03317433D419}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE796D0A-89A6-4DA8-B0A6-E16F7C81C125}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1404,13 +1404,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{08E78BF0-F3C6-4FA0-9F10-5BFC004961C1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{206E160F-C6A0-46D7-BD53-8F44C0161757}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FA6287E7-B9E1-4FFA-874F-F8BA58FF1439}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECA9FD9E-5BC2-43D2-BADA-209D51AFFCEE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE796D0A-89A6-4DA8-B0A6-E16F7C81C125}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{661AFACB-5679-4D56-B2B8-873A0FC13889}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1404,13 +1404,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{206E160F-C6A0-46D7-BD53-8F44C0161757}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CF94376-A734-4069-ADFC-0BAAE0F738F7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECA9FD9E-5BC2-43D2-BADA-209D51AFFCEE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{129F09E6-112C-4DDE-B11F-FCC8016E18DC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{661AFACB-5679-4D56-B2B8-873A0FC13889}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5388448A-DF94-4018-82DE-2B2D878B2D13}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1404,13 +1404,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CF94376-A734-4069-ADFC-0BAAE0F738F7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAD491AE-012C-4CD9-8FBA-80A4A027A9E9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{129F09E6-112C-4DDE-B11F-FCC8016E18DC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EF34693-2247-49E0-A31A-F5AE0DF78312}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5388448A-DF94-4018-82DE-2B2D878B2D13}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0A123A0-4282-41B8-9CA1-71A40A634C94}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1404,13 +1404,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAD491AE-012C-4CD9-8FBA-80A4A027A9E9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7190A3F7-8056-4ABF-B7DF-DEDA5DDAC9C8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5EF34693-2247-49E0-A31A-F5AE0DF78312}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{719B521A-FEF5-498B-9894-94D5C8964741}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0A123A0-4282-41B8-9CA1-71A40A634C94}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3FC97CF-4A85-4E16-90F1-A33DF3F1273E}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1404,13 +1404,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7190A3F7-8056-4ABF-B7DF-DEDA5DDAC9C8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12AE4D06-2B56-4D81-B237-76873566FA2E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{719B521A-FEF5-498B-9894-94D5C8964741}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A9C80A3-C08A-43B3-B8CB-818F39FFF907}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3FC97CF-4A85-4E16-90F1-A33DF3F1273E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67668A2D-B70A-49BE-ACA7-B2B666B9692D}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1404,13 +1404,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12AE4D06-2B56-4D81-B237-76873566FA2E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B530A6FB-1586-4A32-8557-B491B4A485E7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A9C80A3-C08A-43B3-B8CB-818F39FFF907}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA0CD934-729C-4AD2-B9C3-CE5E2C7A19F7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67668A2D-B70A-49BE-ACA7-B2B666B9692D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{162B0366-324F-4B8A-93EE-7F36B7B5D0F4}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1404,13 +1404,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B530A6FB-1586-4A32-8557-B491B4A485E7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DB42DB6-A85C-40EF-8FD0-7041F73BE76D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA0CD934-729C-4AD2-B9C3-CE5E2C7A19F7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DD0A01C-1E40-4CC5-9F68-69C67135713A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{162B0366-324F-4B8A-93EE-7F36B7B5D0F4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BE58AE7-62CF-4D8E-A4CA-8324817EC917}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1404,13 +1404,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DB42DB6-A85C-40EF-8FD0-7041F73BE76D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA1C84B5-C4BB-491E-9988-64FD94509E41}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DD0A01C-1E40-4CC5-9F68-69C67135713A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C24F164-91BC-4347-89AE-1F6DE216CA0D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BE58AE7-62CF-4D8E-A4CA-8324817EC917}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F634C98B-F2BD-4A77-A228-C88A68A6BF23}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1404,13 +1404,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA1C84B5-C4BB-491E-9988-64FD94509E41}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA1FECAB-FC0A-44DF-B83D-C18DB9E1A10E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C24F164-91BC-4347-89AE-1F6DE216CA0D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1276C82C-D32C-4BB3-832C-771BEC2CBC84}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F634C98B-F2BD-4A77-A228-C88A68A6BF23}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41AD9A2A-B84B-4CD6-80CC-33EE7195D4B5}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1404,13 +1404,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA1FECAB-FC0A-44DF-B83D-C18DB9E1A10E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B0C684C-4BCD-4D5F-A85F-B9F6434D3225}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1276C82C-D32C-4BB3-832C-771BEC2CBC84}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B33D2FD9-28E9-4BAE-924B-B7CD8321ABFE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41AD9A2A-B84B-4CD6-80CC-33EE7195D4B5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6B7A3B7-EAB2-482C-800B-4C5540525A92}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1404,13 +1404,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B0C684C-4BCD-4D5F-A85F-B9F6434D3225}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D4170E2-6AD4-4E71-A2F6-4BB73D68525F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B33D2FD9-28E9-4BAE-924B-B7CD8321ABFE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95859796-DDF1-4DA3-9222-842F8E8AE82E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6B7A3B7-EAB2-482C-800B-4C5540525A92}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A630DCB4-2E59-4928-8F4B-AF6DA463A9EF}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1404,13 +1404,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9D4170E2-6AD4-4E71-A2F6-4BB73D68525F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C287202-9253-4724-9DCF-E925A4459A5D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95859796-DDF1-4DA3-9222-842F8E8AE82E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F15BD2FF-992B-4DDF-A7F4-7763B99463AD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A630DCB4-2E59-4928-8F4B-AF6DA463A9EF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11EB4C11-0701-4E76-9C51-9E4F984A6EF7}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1404,13 +1404,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C287202-9253-4724-9DCF-E925A4459A5D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9574916E-B338-4D14-B429-A536D3231A44}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F15BD2FF-992B-4DDF-A7F4-7763B99463AD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B3D7DD6-C86E-4FAB-9065-21452E852486}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11EB4C11-0701-4E76-9C51-9E4F984A6EF7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18BF82D1-7842-429C-95C6-1FA87978E306}"/>
 </file>
--- a/____EvoM1_TraitTable/dexterity_heffner.xlsx
+++ b/____EvoM1_TraitTable/dexterity_heffner.xlsx
@@ -1404,13 +1404,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9574916E-B338-4D14-B429-A536D3231A44}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DECE30B3-FF6C-4D44-AEF9-308066B62324}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B3D7DD6-C86E-4FAB-9065-21452E852486}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{247BB83A-1FBF-4858-8F53-FE8D520846AC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18BF82D1-7842-429C-95C6-1FA87978E306}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DC21814-F6E6-4D25-9305-A2AB0F2046EE}"/>
 </file>